--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DataCuti\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E205A9E6-E817-4C08-A2D7-5FB8FE277A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A81FDC-C2FA-447F-8E19-E63235E97CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{51785488-ACD1-4D6C-967E-7A867C182639}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="14">
   <si>
     <t>Cuti Tahunan</t>
   </si>
@@ -57,64 +57,31 @@
     <t>0 Hari</t>
   </si>
   <si>
-    <t>YOPA AGUSTINA</t>
-  </si>
-  <si>
-    <t>Ada keperluan keluarga</t>
-  </si>
-  <si>
-    <t>Urusan keluarga pulang ke palembang</t>
-  </si>
-  <si>
-    <t>7 Hari</t>
-  </si>
-  <si>
-    <t>ada urusan keluarga (mengambil SKL di MTs Bahrul Ulum Islamic Center Sungai Liat)</t>
-  </si>
-  <si>
-    <t>Ada Keperluan Keluarga</t>
-  </si>
-  <si>
-    <t>ada keperluan keluarga</t>
-  </si>
-  <si>
-    <t>ada urusan keluarga (mengambil rapor anak di Pesantren Islamic Center Sungailiat)</t>
-  </si>
-  <si>
-    <t>.........</t>
-  </si>
-  <si>
-    <t>urusan keluarga</t>
-  </si>
-  <si>
-    <t>..........</t>
-  </si>
-  <si>
-    <t>urusan keluarga (menghantar orang tua dipalembang Umroh)</t>
-  </si>
-  <si>
-    <t>Keperluan Keluarga</t>
-  </si>
-  <si>
-    <t>ada urasan keluarga</t>
-  </si>
-  <si>
-    <t>merawat ibu sakit</t>
-  </si>
-  <si>
-    <t>............</t>
-  </si>
-  <si>
-    <t>Hari Hari</t>
-  </si>
-  <si>
-    <t>Urusan Keluarga</t>
-  </si>
-  <si>
-    <t>................</t>
-  </si>
-  <si>
-    <t>hari Hari</t>
+    <t>LISMASARI</t>
+  </si>
+  <si>
+    <t>Ada acara keluarga.</t>
+  </si>
+  <si>
+    <t>Ada urusan/acara keluarga.</t>
+  </si>
+  <si>
+    <t>8 Hari</t>
+  </si>
+  <si>
+    <t>Ada urusan keluarga dan jemput anak di pondok.</t>
+  </si>
+  <si>
+    <t>Ada urusan keluarga.</t>
+  </si>
+  <si>
+    <t>Menjemput anak di pondok.</t>
+  </si>
+  <si>
+    <t>Ada acara urusan keluarga.</t>
+  </si>
+  <si>
+    <t>Menghadiri acara keluarga.</t>
   </si>
 </sst>
 </file>
@@ -514,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3452293-167E-4EA4-B413-1F0957A25C52}">
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32.453125" style="1" bestFit="1" customWidth="1"/>
@@ -536,16 +503,20 @@
       <c r="C1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3" t="s">
-        <v>2</v>
+      <c r="D1" s="3">
+        <v>850</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="4">
+        <v>46310</v>
       </c>
       <c r="G1" s="4">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="H1" s="4">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>2</v>
@@ -579,13 +550,13 @@
         <v>1</v>
       </c>
       <c r="F2" s="4">
-        <v>46268</v>
+        <v>46286</v>
       </c>
       <c r="G2" s="4">
-        <v>46269</v>
+        <v>46287</v>
       </c>
       <c r="H2" s="4">
-        <v>46272</v>
+        <v>46289</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>8</v>
@@ -619,13 +590,13 @@
         <v>1</v>
       </c>
       <c r="F3" s="4">
-        <v>46178</v>
+        <v>46190</v>
       </c>
       <c r="G3" s="4">
-        <v>46178</v>
+        <v>46191</v>
       </c>
       <c r="H3" s="4">
-        <v>46178</v>
+        <v>46192</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>2</v>
@@ -659,13 +630,13 @@
         <v>1</v>
       </c>
       <c r="F4" s="4">
-        <v>46135</v>
+        <v>46176</v>
       </c>
       <c r="G4" s="4">
-        <v>46135</v>
+        <v>46176</v>
       </c>
       <c r="H4" s="4">
-        <v>46136</v>
+        <v>46176</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>2</v>
@@ -690,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3">
         <v>850</v>
@@ -699,13 +670,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="4">
-        <v>46083</v>
+        <v>46168</v>
       </c>
       <c r="G5" s="4">
-        <v>46084</v>
+        <v>46168</v>
       </c>
       <c r="H5" s="4">
-        <v>46086</v>
+        <v>46168</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>2</v>
@@ -730,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D6" s="3">
         <v>850</v>
@@ -739,13 +710,13 @@
         <v>1</v>
       </c>
       <c r="F6" s="4">
-        <v>46065</v>
+        <v>46163</v>
       </c>
       <c r="G6" s="4">
-        <v>46066</v>
+        <v>46164</v>
       </c>
       <c r="H6" s="4">
-        <v>46066</v>
+        <v>46164</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>2</v>
@@ -770,22 +741,22 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D7" s="3">
         <v>850</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F7" s="4">
-        <v>46009</v>
+        <v>46094</v>
       </c>
       <c r="G7" s="4">
-        <v>46009</v>
+        <v>46094</v>
       </c>
       <c r="H7" s="4">
-        <v>46009</v>
+        <v>46094</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>2</v>
@@ -810,22 +781,22 @@
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D8" s="3">
         <v>850</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="F8" s="4">
-        <v>46002</v>
+        <v>46083</v>
       </c>
       <c r="G8" s="4">
-        <v>46003</v>
+        <v>46085</v>
       </c>
       <c r="H8" s="4">
-        <v>46003</v>
+        <v>46087</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>2</v>
@@ -856,16 +827,16 @@
         <v>850</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F9" s="4">
-        <v>45992</v>
+        <v>46049</v>
       </c>
       <c r="G9" s="4">
-        <v>45993</v>
+        <v>46052</v>
       </c>
       <c r="H9" s="4">
-        <v>45993</v>
+        <v>46052</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>2</v>
@@ -890,22 +861,22 @@
         <v>0</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D10" s="3">
         <v>850</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F10" s="4">
-        <v>45860</v>
+        <v>46008</v>
       </c>
       <c r="G10" s="4">
-        <v>45870</v>
+        <v>46008</v>
       </c>
       <c r="H10" s="4">
-        <v>45877</v>
+        <v>46008</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>2</v>
@@ -930,197 +901,37 @@
         <v>0</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D11" s="3">
         <v>850</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F11" s="4">
-        <v>45812</v>
+        <v>45933</v>
       </c>
       <c r="G11" s="4">
-        <v>45813</v>
+        <v>45933</v>
       </c>
       <c r="H11" s="4">
-        <v>45813</v>
+        <v>45936</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="5" t="s">
         <v>3</v>
       </c>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D12" s="3">
-        <v>857</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="4">
-        <v>45735</v>
-      </c>
-      <c r="G12" s="4">
-        <v>45736</v>
-      </c>
-      <c r="H12" s="4">
-        <v>45736</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D13" s="3">
-        <v>851</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="4">
-        <v>45665</v>
-      </c>
-      <c r="G13" s="4">
-        <v>45665</v>
-      </c>
-      <c r="H13" s="4">
-        <v>45667</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="L13" s="3"/>
-      <c r="M13" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" s="3">
-        <v>851</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="4">
-        <v>45645</v>
-      </c>
-      <c r="G14" s="4">
-        <v>45645</v>
-      </c>
-      <c r="H14" s="4">
-        <v>45645</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="3">
-        <v>851</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F15" s="4">
-        <v>45622</v>
-      </c>
-      <c r="G15" s="4">
-        <v>45622</v>
-      </c>
-      <c r="H15" s="4">
-        <v>45622</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="3"/>
-      <c r="M15" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="N15" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
